--- a/MatrixProfile/results/results_final_final_evaluation/hp_tuning_mp_results_resp_relative.xlsx
+++ b/MatrixProfile/results/results_final_final_evaluation/hp_tuning_mp_results_resp_relative.xlsx
@@ -570,7 +570,7 @@
         <v>739</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="O2" t="n">
         <v>0.196319018404908</v>
@@ -579,10 +579,10 @@
         <v>1.922862376270976</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>0.4878048780487805</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.921726884240714</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         <v>739</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="O3" t="n">
         <v>0.6012269938650306</v>
@@ -644,10 +644,10 @@
         <v>66.80027603675258</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>0.9024390243902439</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>65.62258369063265</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         <v>739</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="O4" t="n">
         <v>0.50920245398773</v>
@@ -709,10 +709,10 @@
         <v>21.94214044683218</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>0.8780487804878049</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>21.22293911505584</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
